--- a/base_prov/amz/amz_abbott_2026-09-02.xlsx
+++ b/base_prov/amz/amz_abbott_2026-09-02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\como se me cante\retail-chatbot-main\eci_abbott-main\base_prov\amz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2062A94E-03BB-4273-A78C-16DE1C456AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CCB5A3-FEA9-4B53-ADDA-D7CBABF8EA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="401">
   <si>
     <t>fecha</t>
   </si>
@@ -148,255 +148,258 @@
     <t>Ensure ProCare - Vainilla, Líquido, Fuente de Proteínas y Nutrición, 30 Pack, 220 ml</t>
   </si>
   <si>
+    <t>KCLIQ</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.mx/dp/B0FCGD42W2</t>
+  </si>
+  <si>
+    <t>NO DISPONIBLE</t>
+  </si>
+  <si>
+    <t>Ensure Advance Café – Formula Nutricional | Pack 16 piezas de 237ml</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>990</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.mx/dp/B0DPLNC1QR</t>
+  </si>
+  <si>
+    <t>Nepro HP - Caja con 24 piezas de 237ml, Sabor Vainilla, Ideal para Pacientes en Diálisis, con Proteínas Escenciales</t>
+  </si>
+  <si>
+    <t>700+ comprados el mes pasado</t>
+  </si>
+  <si>
+    <t>364</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>429</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.mx/dp/B07CN2K5W5</t>
+  </si>
+  <si>
+    <t>Ensure Advance Vainilla – Formula Nutricional | Pack 16 piezas de 237ml</t>
+  </si>
+  <si>
+    <t>1 k+ comprados el mes pasado</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>385</t>
+  </si>
+  <si>
+    <t>874</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.mx/dp/B07CN2GW6C</t>
+  </si>
+  <si>
+    <t>Pedialyte-30 mEq Pepino-Limon Rehidratación Oral Pack 12 de 500 ml</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>1076</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.mx/dp/B0GMS26FTM</t>
+  </si>
+  <si>
+    <t>Pedialyte-30 mEq Piña- Naranja- Rehidratación Oral Pack 12 de 500 ml</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.mx/dp/B0GMRQ4C2M</t>
+  </si>
+  <si>
+    <t>ProSure - en Polvo Sabor Vainilla 380g, para Personas en Tratamiento de Cáncer o Procesos Inflamatorios, Calidad Nutricional, Fuente de Alimentación Especializada</t>
+  </si>
+  <si>
+    <t>100+ comprados el mes pasado</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>1081</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.mx/dp/B07CN6B19W</t>
+  </si>
+  <si>
+    <t>PediaSure Vainilla - Alimentación Especializada Pack 24 de 237 ml</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>716</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.mx/dp/B07CN58J33</t>
+  </si>
+  <si>
+    <t>PediaSure Chocolate - Alimentación Especializada Pack 24 de 237 ml</t>
+  </si>
+  <si>
+    <t>600+ comprados el mes pasado</t>
+  </si>
+  <si>
+    <t>187</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.mx/dp/B07CN6B4R7</t>
+  </si>
+  <si>
+    <t>PediaSure Fresa - Alimentación Especializada Pack 24 de 237 ml</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>718</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.mx/dp/B07CN6BQ8W</t>
+  </si>
+  <si>
+    <t>PediaSure 10+ Vainilla- Alimentación Especializada Pack 24 de 220 ml</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>444</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.mx/dp/B0FDF9Q5Z6</t>
+  </si>
+  <si>
+    <t>Similac Isomil Etapa 1 - 400gr, Fórmula Especializada para Bebés a Base de Proteína de Soya, No Láctea, Nutrición Infantil Equilibrada, con Nucleótidos y Prebióticos, Omega 3 y 6</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.mx/dp/B07CN592FV</t>
+  </si>
+  <si>
+    <t>Similac Isomil Etapa 2 400gr, Fórmula Infantil no Láctea a Base de Proteína de Soya</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.mx/dp/B07CN98DSX</t>
+  </si>
+  <si>
+    <t>PediaSure Vainilla- Alimentación Especializada Polvo 400 g</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>557</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.mx/dp/B0716DZVR3</t>
+  </si>
+  <si>
+    <t>PediaSure MRI - Vainilla en Polvo, 900g, Fórmula Especializada para Niños de 1 a 10 años, Nutrientes Esenciales, Prebióticos, Proteínas, Vitaminas y Minerales, Crecimiento Clínicamente Comprobado</t>
+  </si>
+  <si>
+    <t>468</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.mx/dp/B07CNC5XPD</t>
+  </si>
+  <si>
+    <t>Similac Neosure - 370g, Fórmula Especializada para Bebés Prematuros, con HMO y Hierro, para Lactantes con Necesidades Especiales de Nutrición</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>530</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.mx/dp/B07CN6B8R5</t>
+  </si>
+  <si>
+    <t>PediaSure Chocolate- Alimentación Especializada Polvo 400 g</t>
+  </si>
+  <si>
+    <t>500+ comprados el mes pasado</t>
+  </si>
+  <si>
+    <t>734</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>289</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.mx/dp/B0FCGD42W2</t>
-  </si>
-  <si>
-    <t>Ensure Advance Café – Formula Nutricional | Pack 16 piezas de 237ml</t>
-  </si>
-  <si>
-    <t>152</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>990</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.mx/dp/B0DPLNC1QR</t>
-  </si>
-  <si>
-    <t>Nepro HP - Caja con 24 piezas de 237ml, Sabor Vainilla, Ideal para Pacientes en Diálisis, con Proteínas Escenciales</t>
-  </si>
-  <si>
-    <t>700+ comprados el mes pasado</t>
-  </si>
-  <si>
-    <t>364</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>429</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.mx/dp/B07CN2K5W5</t>
-  </si>
-  <si>
-    <t>Ensure Advance Vainilla – Formula Nutricional | Pack 16 piezas de 237ml</t>
-  </si>
-  <si>
-    <t>1 k+ comprados el mes pasado</t>
-  </si>
-  <si>
-    <t>4.7</t>
-  </si>
-  <si>
-    <t>385</t>
-  </si>
-  <si>
-    <t>874</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.mx/dp/B07CN2GW6C</t>
-  </si>
-  <si>
-    <t>Pedialyte-30 mEq Pepino-Limon Rehidratación Oral Pack 12 de 500 ml</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>1076</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.mx/dp/B0GMS26FTM</t>
-  </si>
-  <si>
-    <t>Pedialyte-30 mEq Piña- Naranja- Rehidratación Oral Pack 12 de 500 ml</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.mx/dp/B0GMRQ4C2M</t>
-  </si>
-  <si>
-    <t>ProSure - en Polvo Sabor Vainilla 380g, para Personas en Tratamiento de Cáncer o Procesos Inflamatorios, Calidad Nutricional, Fuente de Alimentación Especializada</t>
-  </si>
-  <si>
-    <t>100+ comprados el mes pasado</t>
-  </si>
-  <si>
-    <t>271</t>
-  </si>
-  <si>
-    <t>162</t>
-  </si>
-  <si>
-    <t>1081</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.mx/dp/B07CN6B19W</t>
-  </si>
-  <si>
-    <t>PediaSure Vainilla - Alimentación Especializada Pack 24 de 237 ml</t>
-  </si>
-  <si>
-    <t>4.6</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>716</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.mx/dp/B07CN58J33</t>
-  </si>
-  <si>
-    <t>PediaSure Chocolate - Alimentación Especializada Pack 24 de 237 ml</t>
-  </si>
-  <si>
-    <t>600+ comprados el mes pasado</t>
-  </si>
-  <si>
-    <t>187</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.mx/dp/B07CN6B4R7</t>
-  </si>
-  <si>
-    <t>PediaSure Fresa - Alimentación Especializada Pack 24 de 237 ml</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>718</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.mx/dp/B07CN6BQ8W</t>
-  </si>
-  <si>
-    <t>PediaSure 10+ Vainilla- Alimentación Especializada Pack 24 de 220 ml</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>444</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.mx/dp/B0FDF9Q5Z6</t>
-  </si>
-  <si>
-    <t>Similac Isomil Etapa 1 - 400gr, Fórmula Especializada para Bebés a Base de Proteína de Soya, No Láctea, Nutrición Infantil Equilibrada, con Nucleótidos y Prebióticos, Omega 3 y 6</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>178</t>
-  </si>
-  <si>
-    <t>190</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.mx/dp/B07CN592FV</t>
-  </si>
-  <si>
-    <t>Similac Isomil Etapa 2 400gr, Fórmula Infantil no Láctea a Base de Proteína de Soya</t>
-  </si>
-  <si>
-    <t>326</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.mx/dp/B07CN98DSX</t>
-  </si>
-  <si>
-    <t>PediaSure Vainilla- Alimentación Especializada Polvo 400 g</t>
-  </si>
-  <si>
-    <t>215</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>557</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.mx/dp/B0716DZVR3</t>
-  </si>
-  <si>
-    <t>PediaSure MRI - Vainilla en Polvo, 900g, Fórmula Especializada para Niños de 1 a 10 años, Nutrientes Esenciales, Prebióticos, Proteínas, Vitaminas y Minerales, Crecimiento Clínicamente Comprobado</t>
-  </si>
-  <si>
-    <t>468</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.mx/dp/B07CNC5XPD</t>
-  </si>
-  <si>
-    <t>Similac Neosure - 370g, Fórmula Especializada para Bebés Prematuros, con HMO y Hierro, para Lactantes con Necesidades Especiales de Nutrición</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>141</t>
-  </si>
-  <si>
-    <t>530</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.mx/dp/B07CN6B8R5</t>
-  </si>
-  <si>
-    <t>PediaSure Chocolate- Alimentación Especializada Polvo 400 g</t>
-  </si>
-  <si>
-    <t>734</t>
-  </si>
-  <si>
     <t>59</t>
   </si>
   <si>
@@ -436,10 +439,7 @@
     <t>Similac Isomil Etapa 1 - 850g, Fórmula Especializada para Bebés, Nutrición Infantil Equilibrada</t>
   </si>
   <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>203</t>
+    <t>MarLuc</t>
   </si>
   <si>
     <t>https://www.amazon.com.mx/dp/B07CNCFCT5</t>
@@ -508,18 +508,12 @@
     <t>https://www.amazon.com.mx/dp/B0BZQS6S73</t>
   </si>
   <si>
-    <t>NO DISPONIBLE</t>
-  </si>
-  <si>
     <t>https://www.amazon.com.mx/dp/B0BZQTQSJJ</t>
   </si>
   <si>
     <t>Similac Etapa 2 Fórmula de Continuación de 6 a 12 meses 800g</t>
   </si>
   <si>
-    <t>48</t>
-  </si>
-  <si>
     <t>https://www.amazon.com.mx/dp/B0BZQT5BT9</t>
   </si>
   <si>
@@ -568,6 +562,9 @@
     <t>Similac AR Fórmula con Hierro a base de Almidón de Arroz 0 a 12 meses 800g</t>
   </si>
   <si>
+    <t>Vitau Medical</t>
+  </si>
+  <si>
     <t>https://www.amazon.com.mx/dp/B0D4C9H3QG</t>
   </si>
   <si>
@@ -754,9 +751,6 @@
     <t>Ensure Clásico Chocolate – Formula Nutricional | Pack 24 piezas de 237ml</t>
   </si>
   <si>
-    <t>500+ comprados el mes pasado</t>
-  </si>
-  <si>
     <t>147</t>
   </si>
   <si>
@@ -865,10 +859,7 @@
     <t>Ensure Clásico - en Polvo Sabor Vainilla, 400g, Alimentación Especializada con Vitaminas, Proteínas y Prebióticos, Clínicamente Probado</t>
   </si>
   <si>
-    <t>135</t>
-  </si>
-  <si>
-    <t>523</t>
+    <t>Farmacia Prixz</t>
   </si>
   <si>
     <t>https://www.amazon.com.mx/dp/B074KFQM8S</t>
@@ -928,7 +919,7 @@
     <t>Ensure Advance - 16 Pack de 237 ML Cada Uno, Sabor Chocolate, Nutrición Especializada para Adultos</t>
   </si>
   <si>
-    <t>98</t>
+    <t>GAICINI</t>
   </si>
   <si>
     <t>https://www.amazon.com.mx/dp/B07CN58D3Y</t>
@@ -1628,10 +1619,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1675,10 +1666,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -1722,10 +1713,10 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -1769,10 +1760,10 @@
         <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E4" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -1816,40 +1807,19 @@
         <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E5" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" t="s">
         <v>42</v>
       </c>
-      <c r="J5" t="s">
+      <c r="N5" t="s">
         <v>43</v>
       </c>
-      <c r="K5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="O5" t="s">
         <v>44</v>
-      </c>
-      <c r="M5" t="s">
-        <v>45</v>
-      </c>
-      <c r="N5" t="s">
-        <v>46</v>
-      </c>
-      <c r="O5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
@@ -1860,13 +1830,13 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -1878,7 +1848,7 @@
         <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J6" t="s">
         <v>20</v>
@@ -1887,13 +1857,13 @@
         <v>30</v>
       </c>
       <c r="L6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" t="s">
         <v>49</v>
-      </c>
-      <c r="M6" t="s">
-        <v>50</v>
-      </c>
-      <c r="N6" t="s">
-        <v>51</v>
       </c>
       <c r="O6" t="s">
         <v>25</v>
@@ -1907,40 +1877,40 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E7" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H7" t="s">
         <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K7" t="s">
         <v>21</v>
       </c>
       <c r="L7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" t="s">
+        <v>55</v>
+      </c>
+      <c r="N7" t="s">
         <v>56</v>
-      </c>
-      <c r="M7" t="s">
-        <v>57</v>
-      </c>
-      <c r="N7" t="s">
-        <v>58</v>
       </c>
       <c r="O7" t="s">
         <v>25</v>
@@ -1954,25 +1924,25 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" t="s">
+        <v>330</v>
+      </c>
+      <c r="E8" t="s">
+        <v>322</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" t="s">
         <v>59</v>
       </c>
-      <c r="D8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E8" t="s">
-        <v>325</v>
-      </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>60</v>
-      </c>
-      <c r="H8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" t="s">
-        <v>62</v>
       </c>
       <c r="J8" t="s">
         <v>20</v>
@@ -1984,10 +1954,10 @@
         <v>22</v>
       </c>
       <c r="M8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O8" t="s">
         <v>25</v>
@@ -2001,13 +1971,13 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E9" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
@@ -2016,10 +1986,10 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J9" t="s">
         <v>37</v>
@@ -2028,13 +1998,13 @@
         <v>21</v>
       </c>
       <c r="L9" t="s">
+        <v>66</v>
+      </c>
+      <c r="M9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N9" t="s">
         <v>68</v>
-      </c>
-      <c r="M9" t="s">
-        <v>69</v>
-      </c>
-      <c r="N9" t="s">
-        <v>70</v>
       </c>
       <c r="O9" t="s">
         <v>25</v>
@@ -2048,13 +2018,13 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E10" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
@@ -2075,13 +2045,13 @@
         <v>21</v>
       </c>
       <c r="L10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="O10" t="s">
         <v>25</v>
@@ -2095,40 +2065,40 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H11" t="s">
         <v>18</v>
       </c>
       <c r="I11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K11" t="s">
         <v>30</v>
       </c>
       <c r="L11" t="s">
+        <v>75</v>
+      </c>
+      <c r="M11" t="s">
+        <v>76</v>
+      </c>
+      <c r="N11" t="s">
         <v>77</v>
-      </c>
-      <c r="M11" t="s">
-        <v>78</v>
-      </c>
-      <c r="N11" t="s">
-        <v>79</v>
       </c>
       <c r="O11" t="s">
         <v>25</v>
@@ -2142,40 +2112,40 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E12" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
       <c r="G12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I12" t="s">
         <v>38</v>
       </c>
       <c r="J12" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K12" t="s">
         <v>30</v>
       </c>
       <c r="L12" t="s">
+        <v>81</v>
+      </c>
+      <c r="M12" t="s">
         <v>82</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
         <v>83</v>
-      </c>
-      <c r="N12" t="s">
-        <v>84</v>
       </c>
       <c r="O12" t="s">
         <v>25</v>
@@ -2189,40 +2159,40 @@
         <v>14</v>
       </c>
       <c r="C13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" t="s">
+        <v>336</v>
+      </c>
+      <c r="E13" t="s">
+        <v>335</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" t="s">
         <v>85</v>
       </c>
-      <c r="D13" t="s">
-        <v>339</v>
-      </c>
-      <c r="E13" t="s">
-        <v>338</v>
-      </c>
-      <c r="F13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" t="s">
         <v>86</v>
       </c>
-      <c r="H13" t="s">
-        <v>61</v>
-      </c>
-      <c r="I13" t="s">
-        <v>87</v>
-      </c>
       <c r="J13" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K13" t="s">
         <v>30</v>
       </c>
       <c r="L13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O13" t="s">
         <v>25</v>
@@ -2236,13 +2206,13 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E14" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
@@ -2254,22 +2224,22 @@
         <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J14" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K14" t="s">
         <v>30</v>
       </c>
       <c r="L14" t="s">
+        <v>90</v>
+      </c>
+      <c r="M14" t="s">
         <v>91</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>92</v>
-      </c>
-      <c r="N14" t="s">
-        <v>93</v>
       </c>
       <c r="O14" t="s">
         <v>25</v>
@@ -2283,40 +2253,40 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E15" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H15" t="s">
         <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J15" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K15" t="s">
         <v>30</v>
       </c>
       <c r="L15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M15" t="s">
+        <v>95</v>
+      </c>
+      <c r="N15" t="s">
         <v>96</v>
-      </c>
-      <c r="N15" t="s">
-        <v>97</v>
       </c>
       <c r="O15" t="s">
         <v>25</v>
@@ -2330,13 +2300,13 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E16" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
@@ -2345,10 +2315,10 @@
         <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J16" t="s">
         <v>20</v>
@@ -2357,13 +2327,13 @@
         <v>30</v>
       </c>
       <c r="L16" t="s">
+        <v>99</v>
+      </c>
+      <c r="M16" t="s">
         <v>100</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>101</v>
-      </c>
-      <c r="N16" t="s">
-        <v>102</v>
       </c>
       <c r="O16" t="s">
         <v>25</v>
@@ -2377,13 +2347,13 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E17" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
@@ -2392,10 +2362,10 @@
         <v>35</v>
       </c>
       <c r="H17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J17" t="s">
         <v>20</v>
@@ -2404,13 +2374,13 @@
         <v>30</v>
       </c>
       <c r="L17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M17" t="s">
+        <v>104</v>
+      </c>
+      <c r="N17" t="s">
         <v>105</v>
-      </c>
-      <c r="N17" t="s">
-        <v>106</v>
       </c>
       <c r="O17" t="s">
         <v>25</v>
@@ -2424,13 +2394,13 @@
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E18" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
@@ -2442,22 +2412,22 @@
         <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J18" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K18" t="s">
         <v>30</v>
       </c>
       <c r="L18" t="s">
+        <v>108</v>
+      </c>
+      <c r="M18" t="s">
         <v>109</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>110</v>
-      </c>
-      <c r="N18" t="s">
-        <v>111</v>
       </c>
       <c r="O18" t="s">
         <v>25</v>
@@ -2471,13 +2441,13 @@
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D19" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E19" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
@@ -2486,10 +2456,10 @@
         <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J19" t="s">
         <v>36</v>
@@ -2498,13 +2468,13 @@
         <v>30</v>
       </c>
       <c r="L19" t="s">
+        <v>113</v>
+      </c>
+      <c r="M19" t="s">
+        <v>109</v>
+      </c>
+      <c r="N19" t="s">
         <v>114</v>
-      </c>
-      <c r="M19" t="s">
-        <v>110</v>
-      </c>
-      <c r="N19" t="s">
-        <v>115</v>
       </c>
       <c r="O19" t="s">
         <v>25</v>
@@ -2518,13 +2488,13 @@
         <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E20" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
@@ -2533,25 +2503,25 @@
         <v>35</v>
       </c>
       <c r="H20" t="s">
+        <v>116</v>
+      </c>
+      <c r="I20" t="s">
         <v>117</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>118</v>
-      </c>
-      <c r="J20" t="s">
-        <v>119</v>
       </c>
       <c r="K20" t="s">
         <v>30</v>
       </c>
       <c r="L20" t="s">
+        <v>119</v>
+      </c>
+      <c r="M20" t="s">
         <v>120</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>121</v>
-      </c>
-      <c r="N20" t="s">
-        <v>122</v>
       </c>
       <c r="O20" t="s">
         <v>25</v>
@@ -2565,19 +2535,19 @@
         <v>14</v>
       </c>
       <c r="C21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" t="s">
+        <v>345</v>
+      </c>
+      <c r="E21" t="s">
+        <v>335</v>
+      </c>
+      <c r="F21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" t="s">
         <v>123</v>
-      </c>
-      <c r="D21" t="s">
-        <v>348</v>
-      </c>
-      <c r="E21" t="s">
-        <v>338</v>
-      </c>
-      <c r="F21" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" t="s">
-        <v>17</v>
       </c>
       <c r="H21" t="s">
         <v>18</v>
@@ -2586,19 +2556,19 @@
         <v>124</v>
       </c>
       <c r="J21" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="K21" t="s">
         <v>30</v>
       </c>
       <c r="L21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O21" t="s">
         <v>25</v>
@@ -2612,13 +2582,13 @@
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D22" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E22" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F22" t="s">
         <v>16</v>
@@ -2630,22 +2600,22 @@
         <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K22" t="s">
         <v>30</v>
       </c>
       <c r="L22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O22" t="s">
         <v>25</v>
@@ -2659,25 +2629,25 @@
         <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D23" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E23" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F23" t="s">
         <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J23" t="s">
         <v>20</v>
@@ -2686,13 +2656,13 @@
         <v>30</v>
       </c>
       <c r="L23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O23" t="s">
         <v>25</v>
@@ -2706,43 +2676,22 @@
         <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D24" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E24" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24" t="s">
-        <v>35</v>
-      </c>
-      <c r="H24" t="s">
-        <v>61</v>
-      </c>
-      <c r="I24" t="s">
-        <v>138</v>
-      </c>
-      <c r="J24" t="s">
-        <v>20</v>
-      </c>
-      <c r="K24" t="s">
-        <v>21</v>
-      </c>
-      <c r="L24" t="s">
-        <v>90</v>
-      </c>
-      <c r="M24" t="s">
         <v>139</v>
       </c>
       <c r="N24" t="s">
         <v>140</v>
       </c>
       <c r="O24" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
@@ -2756,22 +2705,22 @@
         <v>141</v>
       </c>
       <c r="D25" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E25" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F25" t="s">
         <v>16</v>
       </c>
       <c r="G25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J25" t="s">
         <v>20</v>
@@ -2780,7 +2729,7 @@
         <v>30</v>
       </c>
       <c r="L25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M25" t="s">
         <v>142</v>
@@ -2803,10 +2752,10 @@
         <v>144</v>
       </c>
       <c r="D26" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E26" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F26" t="s">
         <v>16</v>
@@ -2821,16 +2770,16 @@
         <v>35</v>
       </c>
       <c r="J26" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K26" t="s">
         <v>30</v>
       </c>
       <c r="L26" t="s">
+        <v>81</v>
+      </c>
+      <c r="M26" t="s">
         <v>82</v>
-      </c>
-      <c r="M26" t="s">
-        <v>83</v>
       </c>
       <c r="N26" t="s">
         <v>145</v>
@@ -2850,10 +2799,10 @@
         <v>146</v>
       </c>
       <c r="D27" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E27" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F27" t="s">
         <v>16</v>
@@ -2862,22 +2811,22 @@
         <v>35</v>
       </c>
       <c r="H27" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I27" t="s">
         <v>21</v>
       </c>
       <c r="J27" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K27" t="s">
         <v>30</v>
       </c>
       <c r="L27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N27" t="s">
         <v>147</v>
@@ -2897,10 +2846,10 @@
         <v>148</v>
       </c>
       <c r="D28" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E28" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F28" t="s">
         <v>16</v>
@@ -2909,22 +2858,22 @@
         <v>27</v>
       </c>
       <c r="H28" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I28" t="s">
         <v>149</v>
       </c>
       <c r="J28" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="K28" t="s">
         <v>30</v>
       </c>
       <c r="L28" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N28" t="s">
         <v>150</v>
@@ -2944,10 +2893,10 @@
         <v>151</v>
       </c>
       <c r="D29" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E29" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F29" t="s">
         <v>16</v>
@@ -2956,13 +2905,13 @@
         <v>17</v>
       </c>
       <c r="H29" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I29" t="s">
         <v>152</v>
       </c>
       <c r="J29" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K29" t="s">
         <v>30</v>
@@ -2971,7 +2920,7 @@
         <v>153</v>
       </c>
       <c r="M29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N29" t="s">
         <v>154</v>
@@ -2991,10 +2940,10 @@
         <v>155</v>
       </c>
       <c r="D30" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E30" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F30" t="s">
         <v>16</v>
@@ -3035,16 +2984,16 @@
         <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E31" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="N31" t="s">
         <v>161</v>
       </c>
       <c r="O31" t="s">
-        <v>162</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
@@ -3055,16 +3004,16 @@
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="E32" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="N32" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O32" t="s">
-        <v>162</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
@@ -3075,43 +3024,22 @@
         <v>14</v>
       </c>
       <c r="C33" t="s">
+        <v>163</v>
+      </c>
+      <c r="D33" t="s">
+        <v>357</v>
+      </c>
+      <c r="E33" t="s">
+        <v>340</v>
+      </c>
+      <c r="F33" t="s">
+        <v>139</v>
+      </c>
+      <c r="N33" t="s">
         <v>164</v>
       </c>
-      <c r="D33" t="s">
-        <v>360</v>
-      </c>
-      <c r="E33" t="s">
-        <v>343</v>
-      </c>
-      <c r="F33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G33" t="s">
-        <v>35</v>
-      </c>
-      <c r="H33" t="s">
-        <v>117</v>
-      </c>
-      <c r="I33" t="s">
-        <v>165</v>
-      </c>
-      <c r="J33" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" t="s">
-        <v>30</v>
-      </c>
-      <c r="L33" t="s">
-        <v>153</v>
-      </c>
-      <c r="M33" t="s">
-        <v>121</v>
-      </c>
-      <c r="N33" t="s">
-        <v>166</v>
-      </c>
       <c r="O33" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
@@ -3122,13 +3050,13 @@
         <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D34" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E34" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F34" t="s">
         <v>16</v>
@@ -3140,7 +3068,7 @@
         <v>28</v>
       </c>
       <c r="I34" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J34" t="s">
         <v>20</v>
@@ -3149,13 +3077,13 @@
         <v>30</v>
       </c>
       <c r="L34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N34" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="O34" t="s">
         <v>25</v>
@@ -3169,13 +3097,13 @@
         <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D35" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E35" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F35" t="s">
         <v>16</v>
@@ -3187,7 +3115,7 @@
         <v>28</v>
       </c>
       <c r="I35" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J35" t="s">
         <v>20</v>
@@ -3196,13 +3124,13 @@
         <v>30</v>
       </c>
       <c r="L35" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="O35" t="s">
         <v>25</v>
@@ -3216,40 +3144,40 @@
         <v>14</v>
       </c>
       <c r="C36" t="s">
+        <v>170</v>
+      </c>
+      <c r="D36" t="s">
+        <v>360</v>
+      </c>
+      <c r="E36" t="s">
+        <v>335</v>
+      </c>
+      <c r="F36" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H36" t="s">
+        <v>64</v>
+      </c>
+      <c r="I36" t="s">
+        <v>171</v>
+      </c>
+      <c r="J36" t="s">
         <v>172</v>
-      </c>
-      <c r="D36" t="s">
-        <v>363</v>
-      </c>
-      <c r="E36" t="s">
-        <v>338</v>
-      </c>
-      <c r="F36" t="s">
-        <v>16</v>
-      </c>
-      <c r="G36" t="s">
-        <v>75</v>
-      </c>
-      <c r="H36" t="s">
-        <v>66</v>
-      </c>
-      <c r="I36" t="s">
-        <v>173</v>
-      </c>
-      <c r="J36" t="s">
-        <v>174</v>
       </c>
       <c r="K36" t="s">
         <v>21</v>
       </c>
       <c r="L36" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M36" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="N36" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="O36" t="s">
         <v>25</v>
@@ -3263,13 +3191,13 @@
         <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D37" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E37" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F37" t="s">
         <v>16</v>
@@ -3281,7 +3209,7 @@
         <v>156</v>
       </c>
       <c r="I37" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J37" t="s">
         <v>20</v>
@@ -3290,13 +3218,13 @@
         <v>30</v>
       </c>
       <c r="L37" t="s">
+        <v>176</v>
+      </c>
+      <c r="M37" t="s">
+        <v>177</v>
+      </c>
+      <c r="N37" t="s">
         <v>178</v>
-      </c>
-      <c r="M37" t="s">
-        <v>179</v>
-      </c>
-      <c r="N37" t="s">
-        <v>180</v>
       </c>
       <c r="O37" t="s">
         <v>25</v>
@@ -3310,43 +3238,22 @@
         <v>14</v>
       </c>
       <c r="C38" t="s">
+        <v>179</v>
+      </c>
+      <c r="D38" t="s">
+        <v>362</v>
+      </c>
+      <c r="E38" t="s">
+        <v>340</v>
+      </c>
+      <c r="F38" t="s">
+        <v>180</v>
+      </c>
+      <c r="N38" t="s">
         <v>181</v>
       </c>
-      <c r="D38" t="s">
-        <v>365</v>
-      </c>
-      <c r="E38" t="s">
-        <v>343</v>
-      </c>
-      <c r="F38" t="s">
-        <v>16</v>
-      </c>
-      <c r="G38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H38" t="s">
-        <v>156</v>
-      </c>
-      <c r="I38" t="s">
-        <v>173</v>
-      </c>
-      <c r="J38" t="s">
-        <v>20</v>
-      </c>
-      <c r="K38" t="s">
-        <v>30</v>
-      </c>
-      <c r="L38" t="s">
-        <v>178</v>
-      </c>
-      <c r="M38" t="s">
-        <v>179</v>
-      </c>
-      <c r="N38" t="s">
-        <v>182</v>
-      </c>
       <c r="O38" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
@@ -3357,13 +3264,13 @@
         <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D39" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E39" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F39" t="s">
         <v>16</v>
@@ -3372,10 +3279,10 @@
         <v>35</v>
       </c>
       <c r="H39" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I39" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J39" t="s">
         <v>20</v>
@@ -3384,13 +3291,13 @@
         <v>30</v>
       </c>
       <c r="L39" t="s">
+        <v>184</v>
+      </c>
+      <c r="M39" t="s">
+        <v>120</v>
+      </c>
+      <c r="N39" t="s">
         <v>185</v>
-      </c>
-      <c r="M39" t="s">
-        <v>121</v>
-      </c>
-      <c r="N39" t="s">
-        <v>186</v>
       </c>
       <c r="O39" t="s">
         <v>25</v>
@@ -3404,13 +3311,13 @@
         <v>14</v>
       </c>
       <c r="C40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D40" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E40" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F40" t="s">
         <v>16</v>
@@ -3419,10 +3326,10 @@
         <v>35</v>
       </c>
       <c r="H40" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I40" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J40" t="s">
         <v>20</v>
@@ -3431,13 +3338,13 @@
         <v>30</v>
       </c>
       <c r="L40" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M40" t="s">
+        <v>187</v>
+      </c>
+      <c r="N40" t="s">
         <v>188</v>
-      </c>
-      <c r="N40" t="s">
-        <v>189</v>
       </c>
       <c r="O40" t="s">
         <v>25</v>
@@ -3451,13 +3358,13 @@
         <v>14</v>
       </c>
       <c r="C41" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D41" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E41" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F41" t="s">
         <v>16</v>
@@ -3466,10 +3373,10 @@
         <v>35</v>
       </c>
       <c r="H41" t="s">
+        <v>190</v>
+      </c>
+      <c r="I41" t="s">
         <v>191</v>
-      </c>
-      <c r="I41" t="s">
-        <v>192</v>
       </c>
       <c r="J41" t="s">
         <v>20</v>
@@ -3478,13 +3385,13 @@
         <v>30</v>
       </c>
       <c r="L41" t="s">
+        <v>192</v>
+      </c>
+      <c r="M41" t="s">
+        <v>100</v>
+      </c>
+      <c r="N41" t="s">
         <v>193</v>
-      </c>
-      <c r="M41" t="s">
-        <v>101</v>
-      </c>
-      <c r="N41" t="s">
-        <v>194</v>
       </c>
       <c r="O41" t="s">
         <v>25</v>
@@ -3498,13 +3405,13 @@
         <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D42" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E42" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F42" t="s">
         <v>16</v>
@@ -3516,7 +3423,7 @@
         <v>156</v>
       </c>
       <c r="I42" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J42" t="s">
         <v>20</v>
@@ -3525,13 +3432,13 @@
         <v>30</v>
       </c>
       <c r="L42" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M42" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N42" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O42" t="s">
         <v>25</v>
@@ -3545,13 +3452,13 @@
         <v>14</v>
       </c>
       <c r="C43" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D43" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E43" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F43" t="s">
         <v>16</v>
@@ -3563,7 +3470,7 @@
         <v>156</v>
       </c>
       <c r="I43" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J43" t="s">
         <v>20</v>
@@ -3572,13 +3479,13 @@
         <v>30</v>
       </c>
       <c r="L43" t="s">
+        <v>198</v>
+      </c>
+      <c r="M43" t="s">
         <v>199</v>
       </c>
-      <c r="M43" t="s">
+      <c r="N43" t="s">
         <v>200</v>
-      </c>
-      <c r="N43" t="s">
-        <v>201</v>
       </c>
       <c r="O43" t="s">
         <v>25</v>
@@ -3592,25 +3499,25 @@
         <v>14</v>
       </c>
       <c r="C44" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D44" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E44" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F44" t="s">
         <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H44" t="s">
+        <v>190</v>
+      </c>
+      <c r="I44" t="s">
         <v>191</v>
-      </c>
-      <c r="I44" t="s">
-        <v>192</v>
       </c>
       <c r="J44" t="s">
         <v>20</v>
@@ -3619,13 +3526,13 @@
         <v>30</v>
       </c>
       <c r="L44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M44" t="s">
+        <v>202</v>
+      </c>
+      <c r="N44" t="s">
         <v>203</v>
-      </c>
-      <c r="N44" t="s">
-        <v>204</v>
       </c>
       <c r="O44" t="s">
         <v>25</v>
@@ -3639,13 +3546,13 @@
         <v>14</v>
       </c>
       <c r="C45" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D45" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E45" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F45" t="s">
         <v>16</v>
@@ -3657,7 +3564,7 @@
         <v>156</v>
       </c>
       <c r="I45" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J45" t="s">
         <v>20</v>
@@ -3666,13 +3573,13 @@
         <v>30</v>
       </c>
       <c r="L45" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M45" t="s">
+        <v>205</v>
+      </c>
+      <c r="N45" t="s">
         <v>206</v>
-      </c>
-      <c r="N45" t="s">
-        <v>207</v>
       </c>
       <c r="O45" t="s">
         <v>25</v>
@@ -3686,25 +3593,25 @@
         <v>14</v>
       </c>
       <c r="C46" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D46" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E46" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F46" t="s">
         <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H46" t="s">
+        <v>190</v>
+      </c>
+      <c r="I46" t="s">
         <v>191</v>
-      </c>
-      <c r="I46" t="s">
-        <v>192</v>
       </c>
       <c r="J46" t="s">
         <v>20</v>
@@ -3713,13 +3620,13 @@
         <v>30</v>
       </c>
       <c r="L46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M46" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N46" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O46" t="s">
         <v>25</v>
@@ -3733,13 +3640,13 @@
         <v>14</v>
       </c>
       <c r="C47" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D47" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E47" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F47" t="s">
         <v>16</v>
@@ -3748,10 +3655,10 @@
         <v>35</v>
       </c>
       <c r="H47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I47" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J47" t="s">
         <v>20</v>
@@ -3760,13 +3667,13 @@
         <v>30</v>
       </c>
       <c r="L47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M47" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N47" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O47" t="s">
         <v>25</v>
@@ -3780,40 +3687,40 @@
         <v>14</v>
       </c>
       <c r="C48" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D48" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E48" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F48" t="s">
         <v>16</v>
       </c>
       <c r="G48" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H48" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I48" t="s">
         <v>21</v>
       </c>
       <c r="J48" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K48" t="s">
         <v>30</v>
       </c>
       <c r="L48" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M48" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N48" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O48" t="s">
         <v>25</v>
@@ -3827,28 +3734,28 @@
         <v>14</v>
       </c>
       <c r="C49" t="s">
+        <v>214</v>
+      </c>
+      <c r="D49" t="s">
+        <v>373</v>
+      </c>
+      <c r="E49" t="s">
+        <v>335</v>
+      </c>
+      <c r="F49" t="s">
+        <v>16</v>
+      </c>
+      <c r="G49" t="s">
+        <v>134</v>
+      </c>
+      <c r="H49" t="s">
         <v>215</v>
       </c>
-      <c r="D49" t="s">
-        <v>376</v>
-      </c>
-      <c r="E49" t="s">
-        <v>338</v>
-      </c>
-      <c r="F49" t="s">
-        <v>16</v>
-      </c>
-      <c r="G49" t="s">
-        <v>133</v>
-      </c>
-      <c r="H49" t="s">
-        <v>216</v>
-      </c>
       <c r="I49" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J49" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K49" t="s">
         <v>30</v>
@@ -3857,10 +3764,10 @@
         <v>152</v>
       </c>
       <c r="M49" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N49" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O49" t="s">
         <v>25</v>
@@ -3874,19 +3781,19 @@
         <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D50" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E50" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H50" t="s">
         <v>156</v>
@@ -3901,13 +3808,13 @@
         <v>30</v>
       </c>
       <c r="L50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M50" t="s">
+        <v>218</v>
+      </c>
+      <c r="N50" t="s">
         <v>219</v>
-      </c>
-      <c r="N50" t="s">
-        <v>220</v>
       </c>
       <c r="O50" t="s">
         <v>25</v>
@@ -3921,25 +3828,25 @@
         <v>14</v>
       </c>
       <c r="C51" t="s">
+        <v>220</v>
+      </c>
+      <c r="D51" t="s">
+        <v>375</v>
+      </c>
+      <c r="E51" t="s">
+        <v>335</v>
+      </c>
+      <c r="F51" t="s">
+        <v>16</v>
+      </c>
+      <c r="G51" t="s">
         <v>221</v>
       </c>
-      <c r="D51" t="s">
-        <v>378</v>
-      </c>
-      <c r="E51" t="s">
-        <v>338</v>
-      </c>
-      <c r="F51" t="s">
-        <v>16</v>
-      </c>
-      <c r="G51" t="s">
-        <v>222</v>
-      </c>
       <c r="H51" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I51" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J51" t="s">
         <v>37</v>
@@ -3948,13 +3855,13 @@
         <v>30</v>
       </c>
       <c r="L51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M51" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="N51" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O51" t="s">
         <v>25</v>
@@ -3968,13 +3875,13 @@
         <v>14</v>
       </c>
       <c r="C52" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D52" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E52" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F52" t="s">
         <v>16</v>
@@ -3986,22 +3893,22 @@
         <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J52" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="K52" t="s">
         <v>30</v>
       </c>
       <c r="L52" t="s">
+        <v>225</v>
+      </c>
+      <c r="M52" t="s">
         <v>226</v>
       </c>
-      <c r="M52" t="s">
+      <c r="N52" t="s">
         <v>227</v>
-      </c>
-      <c r="N52" t="s">
-        <v>228</v>
       </c>
       <c r="O52" t="s">
         <v>25</v>
@@ -4015,13 +3922,13 @@
         <v>14</v>
       </c>
       <c r="C53" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D53" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E53" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F53" t="s">
         <v>16</v>
@@ -4033,22 +3940,22 @@
         <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J53" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K53" t="s">
         <v>30</v>
       </c>
       <c r="L53" t="s">
+        <v>230</v>
+      </c>
+      <c r="M53" t="s">
         <v>231</v>
       </c>
-      <c r="M53" t="s">
+      <c r="N53" t="s">
         <v>232</v>
-      </c>
-      <c r="N53" t="s">
-        <v>233</v>
       </c>
       <c r="O53" t="s">
         <v>25</v>
@@ -4062,40 +3969,40 @@
         <v>14</v>
       </c>
       <c r="C54" t="s">
+        <v>233</v>
+      </c>
+      <c r="D54" t="s">
+        <v>378</v>
+      </c>
+      <c r="E54" t="s">
+        <v>322</v>
+      </c>
+      <c r="F54" t="s">
+        <v>16</v>
+      </c>
+      <c r="G54" t="s">
         <v>234</v>
       </c>
-      <c r="D54" t="s">
-        <v>381</v>
-      </c>
-      <c r="E54" t="s">
-        <v>325</v>
-      </c>
-      <c r="F54" t="s">
-        <v>16</v>
-      </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
+        <v>59</v>
+      </c>
+      <c r="I54" t="s">
         <v>235</v>
       </c>
-      <c r="H54" t="s">
-        <v>61</v>
-      </c>
-      <c r="I54" t="s">
-        <v>236</v>
-      </c>
       <c r="J54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K54" t="s">
         <v>21</v>
       </c>
       <c r="L54" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M54" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N54" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O54" t="s">
         <v>25</v>
@@ -4109,40 +4016,40 @@
         <v>14</v>
       </c>
       <c r="C55" t="s">
+        <v>237</v>
+      </c>
+      <c r="D55" t="s">
+        <v>379</v>
+      </c>
+      <c r="E55" t="s">
+        <v>322</v>
+      </c>
+      <c r="F55" t="s">
+        <v>16</v>
+      </c>
+      <c r="G55" t="s">
+        <v>73</v>
+      </c>
+      <c r="H55" t="s">
+        <v>59</v>
+      </c>
+      <c r="I55" t="s">
         <v>238</v>
       </c>
-      <c r="D55" t="s">
-        <v>382</v>
-      </c>
-      <c r="E55" t="s">
-        <v>325</v>
-      </c>
-      <c r="F55" t="s">
-        <v>16</v>
-      </c>
-      <c r="G55" t="s">
-        <v>75</v>
-      </c>
-      <c r="H55" t="s">
-        <v>61</v>
-      </c>
-      <c r="I55" t="s">
-        <v>239</v>
-      </c>
       <c r="J55" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="K55" t="s">
         <v>21</v>
       </c>
       <c r="L55" t="s">
+        <v>239</v>
+      </c>
+      <c r="M55" t="s">
         <v>240</v>
       </c>
-      <c r="M55" t="s">
+      <c r="N55" t="s">
         <v>241</v>
-      </c>
-      <c r="N55" t="s">
-        <v>242</v>
       </c>
       <c r="O55" t="s">
         <v>25</v>
@@ -4156,25 +4063,25 @@
         <v>14</v>
       </c>
       <c r="C56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D56" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E56" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F56" t="s">
         <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>244</v>
+        <v>123</v>
       </c>
       <c r="H56" t="s">
         <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="J56" t="s">
         <v>20</v>
@@ -4183,13 +4090,13 @@
         <v>21</v>
       </c>
       <c r="L56" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M56" t="s">
         <v>23</v>
       </c>
       <c r="N56" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="O56" t="s">
         <v>25</v>
@@ -4203,25 +4110,25 @@
         <v>14</v>
       </c>
       <c r="C57" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D57" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E57" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F57" t="s">
         <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H57" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I57" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J57" t="s">
         <v>20</v>
@@ -4230,13 +4137,13 @@
         <v>21</v>
       </c>
       <c r="L57" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M57" t="s">
         <v>23</v>
       </c>
       <c r="N57" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="O57" t="s">
         <v>25</v>
@@ -4250,25 +4157,25 @@
         <v>14</v>
       </c>
       <c r="C58" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D58" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="E58" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F58" t="s">
         <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>244</v>
+        <v>85</v>
       </c>
       <c r="H58" t="s">
         <v>28</v>
       </c>
       <c r="I58" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J58" t="s">
         <v>20</v>
@@ -4277,13 +4184,13 @@
         <v>30</v>
       </c>
       <c r="L58" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M58" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="N58" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="O58" t="s">
         <v>25</v>
@@ -4297,13 +4204,13 @@
         <v>14</v>
       </c>
       <c r="C59" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D59" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E59" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F59" t="s">
         <v>16</v>
@@ -4315,7 +4222,7 @@
         <v>28</v>
       </c>
       <c r="I59" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J59" t="s">
         <v>20</v>
@@ -4324,13 +4231,13 @@
         <v>30</v>
       </c>
       <c r="L59" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M59" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="N59" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="O59" t="s">
         <v>25</v>
@@ -4344,13 +4251,13 @@
         <v>14</v>
       </c>
       <c r="C60" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D60" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E60" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F60" t="s">
         <v>16</v>
@@ -4359,25 +4266,25 @@
         <v>35</v>
       </c>
       <c r="H60" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I60" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="J60" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K60" t="s">
         <v>21</v>
       </c>
       <c r="L60" t="s">
+        <v>258</v>
+      </c>
+      <c r="M60" t="s">
+        <v>259</v>
+      </c>
+      <c r="N60" t="s">
         <v>260</v>
-      </c>
-      <c r="M60" t="s">
-        <v>261</v>
-      </c>
-      <c r="N60" t="s">
-        <v>262</v>
       </c>
       <c r="O60" t="s">
         <v>25</v>
@@ -4391,13 +4298,13 @@
         <v>14</v>
       </c>
       <c r="C61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D61" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E61" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F61" t="s">
         <v>16</v>
@@ -4406,10 +4313,10 @@
         <v>35</v>
       </c>
       <c r="H61" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I61" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J61" t="s">
         <v>37</v>
@@ -4418,13 +4325,13 @@
         <v>21</v>
       </c>
       <c r="L61" t="s">
+        <v>230</v>
+      </c>
+      <c r="M61" t="s">
         <v>231</v>
       </c>
-      <c r="M61" t="s">
-        <v>232</v>
-      </c>
       <c r="N61" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O61" t="s">
         <v>25</v>
@@ -4438,13 +4345,13 @@
         <v>14</v>
       </c>
       <c r="C62" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D62" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E62" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F62" t="s">
         <v>16</v>
@@ -4453,10 +4360,10 @@
         <v>35</v>
       </c>
       <c r="H62" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I62" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="J62" t="s">
         <v>37</v>
@@ -4465,13 +4372,13 @@
         <v>21</v>
       </c>
       <c r="L62" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M62" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="N62" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="O62" t="s">
         <v>25</v>
@@ -4485,13 +4392,13 @@
         <v>14</v>
       </c>
       <c r="C63" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D63" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E63" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F63" t="s">
         <v>16</v>
@@ -4500,25 +4407,25 @@
         <v>35</v>
       </c>
       <c r="H63" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I63" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="J63" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K63" t="s">
         <v>30</v>
       </c>
       <c r="L63" t="s">
+        <v>269</v>
+      </c>
+      <c r="M63" t="s">
+        <v>270</v>
+      </c>
+      <c r="N63" t="s">
         <v>271</v>
-      </c>
-      <c r="M63" t="s">
-        <v>272</v>
-      </c>
-      <c r="N63" t="s">
-        <v>273</v>
       </c>
       <c r="O63" t="s">
         <v>25</v>
@@ -4532,25 +4439,25 @@
         <v>14</v>
       </c>
       <c r="C64" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D64" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E64" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F64" t="s">
         <v>16</v>
       </c>
       <c r="G64" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H64" t="s">
         <v>18</v>
       </c>
       <c r="I64" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J64" t="s">
         <v>20</v>
@@ -4565,7 +4472,7 @@
         <v>32</v>
       </c>
       <c r="N64" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="O64" t="s">
         <v>25</v>
@@ -4579,25 +4486,25 @@
         <v>14</v>
       </c>
       <c r="C65" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D65" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E65" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F65" t="s">
         <v>16</v>
       </c>
       <c r="G65" t="s">
-        <v>222</v>
+        <v>17</v>
       </c>
       <c r="H65" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I65" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J65" t="s">
         <v>20</v>
@@ -4612,7 +4519,7 @@
         <v>23</v>
       </c>
       <c r="N65" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O65" t="s">
         <v>25</v>
@@ -4626,43 +4533,22 @@
         <v>14</v>
       </c>
       <c r="C66" t="s">
+        <v>278</v>
+      </c>
+      <c r="D66" t="s">
+        <v>390</v>
+      </c>
+      <c r="E66" t="s">
+        <v>322</v>
+      </c>
+      <c r="F66" t="s">
+        <v>279</v>
+      </c>
+      <c r="N66" t="s">
         <v>280</v>
       </c>
-      <c r="D66" t="s">
-        <v>393</v>
-      </c>
-      <c r="E66" t="s">
-        <v>325</v>
-      </c>
-      <c r="F66" t="s">
-        <v>16</v>
-      </c>
-      <c r="G66" t="s">
-        <v>35</v>
-      </c>
-      <c r="H66" t="s">
-        <v>61</v>
-      </c>
-      <c r="I66" t="s">
-        <v>203</v>
-      </c>
-      <c r="J66" t="s">
-        <v>43</v>
-      </c>
-      <c r="K66" t="s">
-        <v>30</v>
-      </c>
-      <c r="L66" t="s">
-        <v>281</v>
-      </c>
-      <c r="M66" t="s">
-        <v>282</v>
-      </c>
-      <c r="N66" t="s">
-        <v>283</v>
-      </c>
       <c r="O66" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
@@ -4673,13 +4559,13 @@
         <v>14</v>
       </c>
       <c r="C67" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D67" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E67" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F67" t="s">
         <v>16</v>
@@ -4691,7 +4577,7 @@
         <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="J67" t="s">
         <v>20</v>
@@ -4700,13 +4586,13 @@
         <v>21</v>
       </c>
       <c r="L67" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="M67" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="N67" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="O67" t="s">
         <v>25</v>
@@ -4720,28 +4606,28 @@
         <v>14</v>
       </c>
       <c r="C68" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D68" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E68" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F68" t="s">
         <v>16</v>
       </c>
       <c r="G68" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="J68" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K68" t="s">
         <v>30</v>
@@ -4750,10 +4636,10 @@
         <v>152</v>
       </c>
       <c r="M68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N68" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="O68" t="s">
         <v>25</v>
@@ -4767,40 +4653,40 @@
         <v>14</v>
       </c>
       <c r="C69" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D69" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E69" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F69" t="s">
         <v>16</v>
       </c>
       <c r="G69" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H69" t="s">
         <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="J69" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K69" t="s">
         <v>21</v>
       </c>
       <c r="L69" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="M69" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N69" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="O69" t="s">
         <v>25</v>
@@ -4814,25 +4700,25 @@
         <v>14</v>
       </c>
       <c r="C70" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D70" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E70" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F70" t="s">
         <v>16</v>
       </c>
       <c r="G70" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H70" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I70" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="J70" t="s">
         <v>20</v>
@@ -4841,13 +4727,13 @@
         <v>30</v>
       </c>
       <c r="L70" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="M70" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="N70" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="O70" t="s">
         <v>25</v>
@@ -4861,43 +4747,22 @@
         <v>14</v>
       </c>
       <c r="C71" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D71" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E71" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F71" t="s">
-        <v>16</v>
-      </c>
-      <c r="G71" t="s">
-        <v>35</v>
-      </c>
-      <c r="H71" t="s">
-        <v>18</v>
-      </c>
-      <c r="I71" t="s">
-        <v>139</v>
-      </c>
-      <c r="J71" t="s">
-        <v>20</v>
-      </c>
-      <c r="K71" t="s">
-        <v>21</v>
-      </c>
-      <c r="L71" t="s">
-        <v>302</v>
-      </c>
-      <c r="M71" t="s">
-        <v>50</v>
+        <v>299</v>
       </c>
       <c r="N71" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="O71" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
@@ -4908,40 +4773,40 @@
         <v>14</v>
       </c>
       <c r="C72" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D72" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E72" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F72" t="s">
         <v>16</v>
       </c>
       <c r="G72" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
       </c>
       <c r="I72" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="J72" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K72" t="s">
         <v>30</v>
       </c>
       <c r="L72" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="M72" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N72" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="O72" t="s">
         <v>25</v>
@@ -4955,13 +4820,13 @@
         <v>14</v>
       </c>
       <c r="C73" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D73" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E73" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F73" t="s">
         <v>16</v>
@@ -4973,22 +4838,22 @@
         <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="J73" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K73" t="s">
         <v>30</v>
       </c>
       <c r="L73" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="M73" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="N73" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="O73" t="s">
         <v>25</v>
@@ -5002,13 +4867,13 @@
         <v>14</v>
       </c>
       <c r="C74" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D74" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E74" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F74" t="s">
         <v>16</v>
@@ -5020,22 +4885,22 @@
         <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="J74" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K74" t="s">
         <v>30</v>
       </c>
       <c r="L74" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="M74" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N74" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="O74" t="s">
         <v>25</v>
@@ -5049,13 +4914,13 @@
         <v>14</v>
       </c>
       <c r="C75" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D75" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="E75" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F75" t="s">
         <v>16</v>
@@ -5067,10 +4932,10 @@
         <v>18</v>
       </c>
       <c r="I75" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J75" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K75" t="s">
         <v>30</v>
@@ -5082,7 +4947,7 @@
         <v>32</v>
       </c>
       <c r="N75" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="O75" t="s">
         <v>25</v>
@@ -5096,40 +4961,40 @@
         <v>14</v>
       </c>
       <c r="C76" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D76" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="E76" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F76" t="s">
         <v>16</v>
       </c>
       <c r="G76" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H76" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I76" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="J76" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K76" t="s">
         <v>30</v>
       </c>
       <c r="L76" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M76" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="N76" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="O76" t="s">
         <v>25</v>
